--- a/server/CRM/CRM/wwwroot/UploadFiles/ThongTinTiemNang.xlsx
+++ b/server/CRM/CRM/wwwroot/UploadFiles/ThongTinTiemNang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSIs\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05428B8-396C-4D4E-AC9D-7FAE976720DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CA23FD-DBA8-4336-8E23-DBAA35158034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1752" yWindow="576" windowWidth="21120" windowHeight="10512" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Tên Khách Hàng</t>
   </si>
@@ -106,45 +106,6 @@
   </si>
   <si>
     <t xml:space="preserve">Từ 3 đến 5 tỉ đồng </t>
-  </si>
-  <si>
-    <t>Khách hàng 1</t>
-  </si>
-  <si>
-    <t>Khách hàng 2</t>
-  </si>
-  <si>
-    <t>Khách hàng 3</t>
-  </si>
-  <si>
-    <t>Khách hàng 4</t>
-  </si>
-  <si>
-    <t>Phòng nhân sự</t>
-  </si>
-  <si>
-    <t>Phòng maketing</t>
-  </si>
-  <si>
-    <t>Khách hàng hoặc đối tác giới thiệu</t>
-  </si>
-  <si>
-    <t>Khách hàng doanh nghiệp</t>
-  </si>
-  <si>
-    <t>abc@123</t>
-  </si>
-  <si>
-    <t>abc@456</t>
-  </si>
-  <si>
-    <t>abc@789</t>
-  </si>
-  <si>
-    <t>Doanh nghiệp</t>
-  </si>
-  <si>
-    <t>Khác</t>
   </si>
 </sst>
 </file>
@@ -154,7 +115,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,14 +136,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -201,19 +154,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -526,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87B1377-5947-465F-93BB-487646B99284}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
@@ -644,113 +594,31 @@
         <v>40544</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100" xr:uid="{FD2B4EA1-D9D4-4402-85EF-3B355AF48B83}">
-      <formula1>"Phòng giám đốc,Phòng tài chính,Phòng nhân sự,Phòng maketing,Phòng chăm sóc khách hàng,Phòng kinh doanh"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
-      <formula1>"Nhân viên kinh doanh tự tìm kiếm,Khách hàng hoặc đối tác giới thiệu,Thông qua sự kiện hội thảo tập huấn,Khách hàng tự tìm đến,Marketing,Khác"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F28" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
-      <formula1>"Khách hàng bán lẻ,Khách hàng doanh nghiệp"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L100" xr:uid="{9F0A8666-D5BD-40B7-A821-DA2EFD890D38}">
-      <formula1>"Doanh nghiệp,Cá nhân ,Khác"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M100" xr:uid="{830D9541-9704-49E3-84FE-A54926A2CA82}">
-      <formula1>"Thương mại"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N100" xr:uid="{E4EE7E7B-BE2F-475B-8863-A35DBA405826}">
-      <formula1>"Kinh doanh thực phẩm , kinh doanh hóa mĩ phẩm ,Kinh doanh điện tử điện lạnh, kinh doanh đồ gỗ, Kinh doanh hàng gia dụng , kinh doanh nông sản,Kinh doanh sắt thép , kinh doanh thương mại khác"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{0869C82E-FE33-4E08-BB8A-9FEBB18F4208}">
       <formula1>"Dưới 1 tỉ đồng , 1 tỉ đồng đến 3 tỉ đồng ,Từ 3 đến 5 tỉ đồng ,Trên 5 tỉ đồng"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B96" xr:uid="{FD2B4EA1-D9D4-4402-85EF-3B355AF48B83}">
+      <formula1>"Phòng giám đốc,Phòng tài chính,Phòng nhân sự,Phòng maketing,Phòng chăm sóc khách hàng,Phòng kinh doanh"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E96" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
+      <formula1>"Nhân viên kinh doanh tự tìm kiếm,Khách hàng hoặc đối tác giới thiệu,Thông qua sự kiện hội thảo tập huấn,Khách hàng tự tìm đến,Marketing,Khác"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F24" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
+      <formula1>"Khách hàng bán lẻ,Khách hàng doanh nghiệp"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L96" xr:uid="{9F0A8666-D5BD-40B7-A821-DA2EFD890D38}">
+      <formula1>"Doanh nghiệp,Cá nhân ,Khác"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M96" xr:uid="{830D9541-9704-49E3-84FE-A54926A2CA82}">
+      <formula1>"Thương mại"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N96" xr:uid="{E4EE7E7B-BE2F-475B-8863-A35DBA405826}">
+      <formula1>"Kinh doanh thực phẩm , kinh doanh hóa mĩ phẩm ,Kinh doanh điện tử điện lạnh, kinh doanh đồ gỗ, Kinh doanh hàng gia dụng , kinh doanh nông sản,Kinh doanh sắt thép , kinh doanh thương mại khác"</formula1>
+    </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{E64EB9F2-A21A-4886-AE5E-BE5E6B8B718E}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{2329BA09-7E98-4C9C-B4A0-CCAA307E001F}"/>
-    <hyperlink ref="H5" r:id="rId3" xr:uid="{00CBC328-05B6-4349-93ED-0A6CEE52EC38}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/server/CRM/CRM/wwwroot/UploadFiles/ThongTinTiemNang.xlsx
+++ b/server/CRM/CRM/wwwroot/UploadFiles/ThongTinTiemNang.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSIs\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyInterval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF2F5E9-0CAF-4DFA-985F-9EC4D8021A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99DC3C95-730D-4C73-927C-959B1E77CC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Tên Khách Hàng</t>
   </si>
@@ -81,7 +81,7 @@
     <t>Thông tin mô tả</t>
   </si>
   <si>
-    <t>Khách hàng 1</t>
+    <t>Khách hàng test 1</t>
   </si>
   <si>
     <t>Nhân viên kinh doanh tự tìm kiếm</t>
@@ -90,55 +90,55 @@
     <t>Khách hàng bán lẻ</t>
   </si>
   <si>
-    <t>test@123</t>
-  </si>
-  <si>
-    <t>Khách hàng 2</t>
-  </si>
-  <si>
-    <t>Khách hàng 3</t>
-  </si>
-  <si>
-    <t>Khách hàng 4</t>
-  </si>
-  <si>
-    <t>Khách hàng 5</t>
-  </si>
-  <si>
-    <t>Khách hàng 6</t>
-  </si>
-  <si>
-    <t>Khách hàng 7</t>
-  </si>
-  <si>
-    <t>Khách hàng 8</t>
-  </si>
-  <si>
-    <t>Khách hàng 9</t>
-  </si>
-  <si>
-    <t>test@124</t>
-  </si>
-  <si>
-    <t>test@125</t>
-  </si>
-  <si>
-    <t>test@126</t>
-  </si>
-  <si>
-    <t>test@127</t>
-  </si>
-  <si>
-    <t>test@128</t>
-  </si>
-  <si>
-    <t>test@129</t>
-  </si>
-  <si>
-    <t>test@130</t>
-  </si>
-  <si>
-    <t>test@131</t>
+    <t>Khách hàng test 2</t>
+  </si>
+  <si>
+    <t>Khách hàng test 3</t>
+  </si>
+  <si>
+    <t>Khách hàng test 4</t>
+  </si>
+  <si>
+    <t>Khách hàng test 5</t>
+  </si>
+  <si>
+    <t>Khách hàng test 6</t>
+  </si>
+  <si>
+    <t>Khách hàng test 7</t>
+  </si>
+  <si>
+    <t>Khách hàng test 8</t>
+  </si>
+  <si>
+    <t>Khách hàng test 9</t>
+  </si>
+  <si>
+    <t>email@123</t>
+  </si>
+  <si>
+    <t>email@124</t>
+  </si>
+  <si>
+    <t>email@125</t>
+  </si>
+  <si>
+    <t>email@126</t>
+  </si>
+  <si>
+    <t>email@127</t>
+  </si>
+  <si>
+    <t>email@128</t>
+  </si>
+  <si>
+    <t>email@129</t>
+  </si>
+  <si>
+    <t>email@130</t>
+  </si>
+  <si>
+    <t>email@131</t>
   </si>
 </sst>
 </file>
@@ -170,15 +170,15 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -203,14 +203,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -527,30 +527,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87B1377-5947-465F-93BB-487646B99284}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.5546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,12 +606,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="2">
-        <v>78123812</v>
+        <v>123210931</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>19</v>
@@ -620,148 +620,100 @@
         <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C3" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>78123812</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>123210931</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100" xr:uid="{FD2B4EA1-D9D4-4402-85EF-3B355AF48B83}">
       <formula1>"Phòng giám đốc,Phòng tài chính,Phòng nhân sự,Phòng maketing,Phòng chăm sóc khách hàng,Phòng kinh doanh"</formula1>
@@ -769,7 +721,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
       <formula1>"Nhân viên kinh doanh tự tìm kiếm,Khách hàng hoặc đối tác giới thiệu,Thông qua sự kiện hội thảo tập huấn,Khách hàng tự tìm đến,Marketing,Khác"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F10" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
       <formula1>"Khách hàng bán lẻ,Khách hàng doanh nghiệp"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L100" xr:uid="{9F0A8666-D5BD-40B7-A821-DA2EFD890D38}">
@@ -786,8 +738,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{84899E9F-D607-45D4-BB32-104541A701C2}"/>
-    <hyperlink ref="H3:H10" r:id="rId2" display="test@123" xr:uid="{64340B1E-222A-4132-BED4-AE4211FA4919}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{0526D9EB-81FE-4B03-9AB0-041ED5C63BEA}"/>
+    <hyperlink ref="H3:H10" r:id="rId2" display="email@123" xr:uid="{7C27892F-9974-4DF3-ACF9-89B77569540A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
